--- a/public/freshy2026_scores.xlsx
+++ b/public/freshy2026_scores.xlsx
@@ -960,30 +960,30 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
+      <c r="C3" s="2">
+        <v>56</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2">
+        <v>56</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1876,16 +1876,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -1906,10 +1906,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>11.2</v>
       </c>
       <c r="N5" t="s">
         <v>85</v>
@@ -1920,10 +1920,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>82</v>

--- a/public/freshy2026_scores.xlsx
+++ b/public/freshy2026_scores.xlsx
@@ -9,14 +9,15 @@
     <sheet sheetId="3" name="Miss Queen" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Miss Congeniality" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="Miss Jumbo" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="🏆 ผลการตัดสินรอบ TOP 5" state="visible" r:id="rId9"/>
+    <sheet sheetId="6" name="⚡ ผลรอบ TOP 5 (Speed)" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="🏆 ผลการตัดสินชี้ขาด (Official)" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>รหัส</t>
   </si>
@@ -24,19 +25,13 @@
     <t>ชื่อ-นามสกุล</t>
   </si>
   <si>
-    <t>แนะนำตัว (รวม 5 ก.)</t>
-  </si>
-  <si>
-    <t>Grand Opening (รวม 5 ก.)</t>
-  </si>
-  <si>
-    <t>Speech 1 min (รวม 5 ก.)</t>
-  </si>
-  <si>
-    <t>ชุดธีม (รวม 5 ก.)</t>
-  </si>
-  <si>
-    <t>คะแนนรวมรอบ 29 คน</t>
+    <t>1. ห้องดำ (รวม 5 ก. เต็ม 125)</t>
+  </si>
+  <si>
+    <t>2. Grand Opening (รวม 5 ก. เต็ม 250)</t>
+  </si>
+  <si>
+    <t>คะแนนรวม 2 รอบแรก (เต็ม 375)</t>
   </si>
   <si>
     <t>สถานะ TOP 5</t>
@@ -48,7 +43,7 @@
     <t>นาย พงศกร วรวิทย์ (มาร์ค)</t>
   </si>
   <si>
-    <t>⭐ ผ่านเข้ารอบ 5 คนสุดท้าย (Top 5 คะแนนสูงสุด)</t>
+    <t>⭐ ผ่านเข้ารอบ TOP 5 (Speed)</t>
   </si>
   <si>
     <t>M2</t>
@@ -222,61 +217,82 @@
     <t>น.ส. วรัญญา สิริโภคา (น้ำหวาน)</t>
   </si>
   <si>
+    <t>อันดับ Speed</t>
+  </si>
+  <si>
+    <t>หมวดหมู่</t>
+  </si>
+  <si>
+    <t>คะแนน 2 รอบแรก (375)</t>
+  </si>
+  <si>
+    <t>Speed ก.1 (50)</t>
+  </si>
+  <si>
+    <t>Speed ก.2 (50)</t>
+  </si>
+  <si>
+    <t>Speed ก.3 (50)</t>
+  </si>
+  <si>
+    <t>Speed ก.4 (50)</t>
+  </si>
+  <si>
+    <t>Speed ก.5 (50)</t>
+  </si>
+  <si>
+    <t>รวม Speed (250)</t>
+  </si>
+  <si>
+    <t>สถานะ TOP 3</t>
+  </si>
+  <si>
+    <t>Mister</t>
+  </si>
+  <si>
+    <t>รองชนะเลิศอันดับ 4</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
+    <t>รองชนะเลิศอันดับ 3</t>
+  </si>
+  <si>
     <t>อันดับ</t>
   </si>
   <si>
-    <t>หมวดหมู่</t>
-  </si>
-  <si>
-    <t>คะแนนรอบ 29 คน (รวม 5 ก.)</t>
-  </si>
-  <si>
-    <t>ตอบคำถาม ก.1</t>
-  </si>
-  <si>
-    <t>ตอบคำถาม ก.2</t>
-  </si>
-  <si>
-    <t>ตอบคำถาม ก.3</t>
-  </si>
-  <si>
-    <t>ตอบคำถาม ก.4</t>
-  </si>
-  <si>
-    <t>ตอบคำถาม ก.5</t>
-  </si>
-  <si>
-    <t>รวมตอบคำถาม</t>
-  </si>
-  <si>
-    <t>คะแนนรวมสุทธิ</t>
-  </si>
-  <si>
-    <t>คะแนนเฉลี่ยสุทธิ (หาร 5 กรรมการ)</t>
-  </si>
-  <si>
-    <t>รางวัล</t>
-  </si>
-  <si>
-    <t>Miss</t>
+    <t>ตอบคำถาม ก.1 (100)</t>
+  </si>
+  <si>
+    <t>ตอบคำถาม ก.2 (100)</t>
+  </si>
+  <si>
+    <t>ตอบคำถาม ก.3 (100)</t>
+  </si>
+  <si>
+    <t>ตอบคำถาม ก.4 (100)</t>
+  </si>
+  <si>
+    <t>ตอบคำถาม ก.5 (100)</t>
+  </si>
+  <si>
+    <t>รวมตอบคำถาม (500)</t>
+  </si>
+  <si>
+    <t>คะแนนเฉลี่ยสุทธิ (100)</t>
+  </si>
+  <si>
+    <t>รางวัลเกียรติยศ</t>
   </si>
   <si>
     <t>👑 ชนะเลิศ THE WINNER FRESHY 2026</t>
   </si>
   <si>
-    <t>Mister</t>
-  </si>
-  <si>
     <t>🥈 รองชนะเลิศอันดับ 1</t>
   </si>
   <si>
     <t>🥉 รองชนะเลิศอันดับ 2</t>
-  </si>
-  <si>
-    <t>รองชนะเลิศอันดับ 3</t>
-  </si>
-  <si>
-    <t>รองชนะเลิศอันดับ 4</t>
   </si>
 </sst>
 </file>
@@ -303,7 +319,7 @@
       <color rgb="FF111FA2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,6 +334,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E3A8A"/>
       </patternFill>
     </fill>
     <fill>
@@ -343,16 +364,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,20 +716,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -724,150 +746,114 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" s="2">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="D2" s="2">
         <v>90</v>
       </c>
       <c r="E2" s="2">
-        <v>89</v>
-      </c>
-      <c r="F2" s="2">
-        <v>95</v>
-      </c>
-      <c r="G2" s="2">
-        <v>369</v>
-      </c>
-      <c r="H2" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="C3" s="2">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
         <v>88</v>
       </c>
       <c r="E3" s="2">
-        <v>84</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>260</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
       <c r="C7">
         <v>0</v>
       </c>
@@ -877,14 +863,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
+      <c r="F7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -895,20 +875,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -927,22 +905,16 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
         <v>95</v>
@@ -950,127 +922,97 @@
       <c r="E2" s="2">
         <v>95</v>
       </c>
-      <c r="F2" s="2">
-        <v>94</v>
-      </c>
-      <c r="G2" s="2">
-        <v>384</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2">
-        <v>56</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0</v>
-      </c>
-      <c r="G3" s="2">
-        <v>56</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>27</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>29</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>30</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
-      </c>
       <c r="C7">
         <v>0</v>
       </c>
@@ -1080,14 +1022,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
+      <c r="F7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1098,20 +1034,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1130,150 +1064,114 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>37</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>38</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>39</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>41</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>43</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
       <c r="C7">
         <v>0</v>
       </c>
@@ -1283,14 +1181,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
+      <c r="F7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1301,20 +1193,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1333,150 +1223,114 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>46</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>47</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>48</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>49</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>50</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>51</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>52</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>53</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>54</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>55</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
       <c r="C7">
         <v>0</v>
       </c>
@@ -1486,14 +1340,8 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
+      <c r="F7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1504,20 +1352,18 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="20" customWidth="1"/>
-    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
+    <col min="6" max="6" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1536,124 +1382,94 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>58</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>59</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>60</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>61</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>62</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>63</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>64</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>65</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
       <c r="C6">
         <v>0</v>
       </c>
@@ -1663,14 +1479,8 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6" t="s">
-        <v>15</v>
+      <c r="F6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1681,167 +1491,395 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2">
+        <v>115</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3">
+        <v>95</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4">
+        <v>88</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="28" customWidth="1"/>
-    <col min="14" max="14" width="25" customWidth="1"/>
+    <col min="4" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="12" max="12" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
+    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="M1" s="3" t="s">
+      <c r="D1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="4">
-        <v>384</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="E2" s="5">
         <v>97</v>
       </c>
-      <c r="G2" s="4">
-        <v>0</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0</v>
-      </c>
-      <c r="I2" s="4">
-        <v>0</v>
-      </c>
-      <c r="J2" s="4">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4">
+      <c r="F2" s="5">
+        <v>0</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
         <v>97</v>
       </c>
-      <c r="L2" s="4">
-        <v>481</v>
-      </c>
-      <c r="M2" s="4">
-        <v>96.2</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K2" s="5">
+        <v>19.4</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E3">
-        <v>369</v>
+        <v>94</v>
       </c>
       <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
         <v>94</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
       <c r="K3">
-        <v>94</v>
-      </c>
-      <c r="L3">
-        <v>463</v>
-      </c>
-      <c r="M3">
-        <v>92.6</v>
-      </c>
-      <c r="N3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+        <v>18.8</v>
+      </c>
+      <c r="L3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E4">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -1861,102 +1899,84 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
-        <v>260</v>
-      </c>
-      <c r="M4">
-        <v>52</v>
-      </c>
-      <c r="N4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
-      </c>
-      <c r="E5">
-        <v>56</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>56</v>
-      </c>
-      <c r="M5">
-        <v>11.2</v>
-      </c>
-      <c r="N5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>86</v>
+        <v>76</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/public/freshy2026_scores.xlsx
+++ b/public/freshy2026_scores.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="93">
   <si>
     <t>รหัส</t>
   </si>
@@ -37,21 +37,21 @@
     <t>สถานะ TOP 5</t>
   </si>
   <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>นาย ธีรภัทร ศิริวัฒน์ (เจมส์)</t>
+  </si>
+  <si>
+    <t>⭐ ผ่านเข้ารอบ TOP 5 (Speed)</t>
+  </si>
+  <si>
     <t>M1</t>
   </si>
   <si>
     <t>นาย พงศกร วรวิทย์ (มาร์ค)</t>
   </si>
   <si>
-    <t>⭐ ผ่านเข้ารอบ TOP 5 (Speed)</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>นาย ธีรภัทร ศิริวัฒน์ (เจมส์)</t>
-  </si>
-  <si>
     <t>M3</t>
   </si>
   <si>
@@ -250,10 +250,13 @@
     <t>Mister</t>
   </si>
   <si>
+    <t>👑 ผ่านเข้ารอบ TOP 3 ตัดสิน</t>
+  </si>
+  <si>
+    <t>Miss</t>
+  </si>
+  <si>
     <t>รองชนะเลิศอันดับ 4</t>
-  </si>
-  <si>
-    <t>Miss</t>
   </si>
   <si>
     <t>รองชนะเลิศอันดับ 3</t>
@@ -319,7 +322,7 @@
       <color rgb="FF111FA2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,6 +342,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0E7FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -364,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -373,10 +381,11 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,13 +764,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" s="2">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>8</v>
@@ -775,13 +784,13 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D3" s="2">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -1542,41 +1551,41 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E2">
-        <v>115</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="E2" s="4">
+        <v>75</v>
+      </c>
+      <c r="F2" s="4">
+        <v>50</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>50</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1615,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1623,10 +1632,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
         <v>76</v>
@@ -1653,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1691,7 +1700,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1729,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1751,80 +1760,80 @@
     <col min="12" max="12" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="K1" s="5" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="L1" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="6">
+        <v>100</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0</v>
+      </c>
+      <c r="J2" s="6">
+        <v>100</v>
+      </c>
+      <c r="K2" s="6">
         <v>20</v>
       </c>
-      <c r="C2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" s="5">
-        <v>97</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>0</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="5">
-        <v>97</v>
-      </c>
-      <c r="K2" s="5">
-        <v>19.4</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>89</v>
+      <c r="L2" s="6" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -1832,16 +1841,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E3">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1856,13 +1865,13 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K3">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="L3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -1870,10 +1879,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D4" t="s">
         <v>76</v>
@@ -1900,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -1938,7 +1947,7 @@
         <v>13</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -1976,7 +1985,7 @@
         <v>13</v>
       </c>
       <c r="L6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
